--- a/Knowledge_Repository/Knowledge_Base.xlsx
+++ b/Knowledge_Repository/Knowledge_Base.xlsx
@@ -1,45 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hksdap-my.sharepoint.com/personal/isaac_ng_sdap_com_hk/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{7BCCF25E-11A2-4F3F-B0A7-4A0AD20B3AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="13080" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{F5A995C7-A96B-48AF-93E0-EB27A17CBB60}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="850">
   <si>
     <t>ID</t>
   </si>
@@ -143,6 +139,24 @@
     <t>Security Awareness</t>
   </si>
   <si>
+    <t>HKCGI Q2 2026 Phishing Campaign Report</t>
+  </si>
+  <si>
+    <t>Need to assess user phishing awareness and measure employee response to phishing simulations</t>
+  </si>
+  <si>
+    <t>Ongoing phishing threats require continuous awareness assessment and security training among employees</t>
+  </si>
+  <si>
+    <t>Continue phishing simulations, provide targeted remediation training, monitor user behaviour, and expand phishing template diversity</t>
+  </si>
+  <si>
+    <t>Phishing,SAT,SecurityAwareness,Training,Cybersecurity</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>KB005</t>
   </si>
   <si>
@@ -152,6 +166,18 @@
     <t>CWB_CSO4 Low Disk Space Alert</t>
   </si>
   <si>
+    <t>Workstation C drive free space dropped below monitoring threshold (9% free)</t>
+  </si>
+  <si>
+    <t>Insufficient available storage capacity on endpoint due to accumulated files and storage consumption</t>
+  </si>
+  <si>
+    <t>Perform workstation analysis, identify large files, remove unnecessary data, archive old content, and optimise storage usage</t>
+  </si>
+  <si>
+    <t>DiskSpace,Storage,RMM,Monitoring,Workstation,AEM</t>
+  </si>
+  <si>
     <t>KB006</t>
   </si>
   <si>
@@ -161,141 +187,165 @@
     <t>Unauthorized Use of Company Information</t>
   </si>
   <si>
+    <t>Third-party website used company information and contact details without authorization</t>
+  </si>
+  <si>
+    <t>Fraudulent website impersonated company identity and misused official corporate information for potential scam activities</t>
+  </si>
+  <si>
+    <t>Issue public advisory, notify customers, monitor abuse, report fraudulent activity, and cooperate with authorities</t>
+  </si>
+  <si>
+    <t>Fraud,Scam,Impersonation,BrandProtection,SecurityAdvisory</t>
+  </si>
+  <si>
+    <t>Official Notice</t>
+  </si>
+  <si>
     <t>KB007</t>
   </si>
   <si>
+    <t>Network Troubleshooting</t>
+  </si>
+  <si>
+    <t>Serious Network Problem During Conference Calls</t>
+  </si>
+  <si>
+    <t>Users experienced poor audio/video quality and unstable connectivity during conference calls, impacting communication and collaboration</t>
+  </si>
+  <si>
+    <t>Network performance degradation potentially caused by insufficient bandwidth, latency, packet loss, wireless instability, or infrastructure configuration issues</t>
+  </si>
+  <si>
+    <t>Perform network diagnostics, test bandwidth utilization, verify switch and firewall configurations, monitor latency and packet loss, optimize network paths, and implement continuous monitoring</t>
+  </si>
+  <si>
+    <t>Network,ConferenceCall,VoIP,Teams,Bandwidth,Latency,PacketLoss,Troubleshooting</t>
+  </si>
+  <si>
+    <t>SDAP (Internal) - PDGM, MSP, Serious network problem for doing conference call, v20260708.eml</t>
+  </si>
+  <si>
     <t>KB008</t>
   </si>
   <si>
+    <t>Suspicious Network Activity Detected by MDR</t>
+  </si>
+  <si>
+    <t>MDR platform detected abnormal network activity associated with a monitored endpoint, indicating possible unauthorized communication or compromise</t>
+  </si>
+  <si>
+    <t>Suspicious outbound or inbound network traffic triggered threat detection rules and required investigation to determine legitimacy and potential security impact</t>
+  </si>
+  <si>
+    <t>Review MDR alerts, investigate network connections, validate user activity, perform threat hunting, isolate affected endpoint if necessary, and implement remediation actions based on findings</t>
+  </si>
+  <si>
+    <t>MDR,NetworkActivity,SecurityIncident,ThreatHunting,EDR,Cybersecurity,Investigation</t>
+  </si>
+  <si>
+    <t>SDAP - OTEL, MSP, MDR Alert (Jackie Tsang, 10.255.70.57, Suspicious Network Activity), v20260706.eml</t>
+  </si>
+  <si>
     <t>KB009</t>
   </si>
   <si>
+    <t>BBG-CN Disk Utilisation Alert</t>
+  </si>
+  <si>
+    <t>Server or workstation storage utilization exceeded predefined monitoring thresholds and may impact system performance or operations</t>
+  </si>
+  <si>
+    <t>Excessive disk consumption caused by large files, application data growth, log accumulation, backups, or insufficient storage allocation</t>
+  </si>
+  <si>
+    <t>Analyze disk usage, identify storage-consuming directories, remove unnecessary files, archive historical data, increase storage capacity if required, and implement storage monitoring</t>
+  </si>
+  <si>
+    <t>DiskUtilisation,Storage,Monitoring,RMM,Server,CapacityManagement,CloudAlpha</t>
+  </si>
+  <si>
+    <t>SDAP - CloudAlpha, MSP, Monitoring Alert (BBG-CN, BBG-CN_admin, Disk Utilisation), v20260706.eml</t>
+  </si>
+  <si>
     <t>KB010</t>
   </si>
   <si>
-    <t>HKCGI Q2 2026 Phishing Campaign Report</t>
-  </si>
-  <si>
-    <t>Need to assess user phishing awareness and measure employee response to phishing simulations</t>
-  </si>
-  <si>
-    <t>Ongoing phishing threats require continuous awareness assessment and security training among employees</t>
-  </si>
-  <si>
-    <t>Continue phishing simulations, provide targeted remediation training, monitor user behaviour, and expand phishing template diversity</t>
-  </si>
-  <si>
-    <t>Phishing,SAT,SecurityAwareness,Training,Cybersecurity</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Workstation C drive free space dropped below monitoring threshold (9% free)</t>
-  </si>
-  <si>
-    <t>Insufficient available storage capacity on endpoint due to accumulated files and storage consumption</t>
-  </si>
-  <si>
-    <t>Perform workstation analysis, identify large files, remove unnecessary data, archive old content, and optimise storage usage</t>
-  </si>
-  <si>
-    <t>DiskSpace,Storage,RMM,Monitoring,Workstation,AEM</t>
-  </si>
-  <si>
-    <t>Third-party website used company information and contact details without authorization</t>
-  </si>
-  <si>
-    <t>Fraudulent website impersonated company identity and misused official corporate information for potential scam activities</t>
-  </si>
-  <si>
-    <t>Issue public advisory, notify customers, monitor abuse, report fraudulent activity, and cooperate with authorities</t>
-  </si>
-  <si>
-    <t>Fraud,Scam,Impersonation,BrandProtection,SecurityAdvisory</t>
-  </si>
-  <si>
-    <t>Official Notice</t>
-  </si>
-  <si>
-    <t>Network Troubleshooting</t>
-  </si>
-  <si>
-    <t>Serious Network Problem During Conference Calls</t>
-  </si>
-  <si>
-    <t>Users experienced poor audio/video quality and unstable connectivity during conference calls, impacting communication and collaboration</t>
-  </si>
-  <si>
-    <t>Network performance degradation potentially caused by insufficient bandwidth, latency, packet loss, wireless instability, or infrastructure configuration issues</t>
-  </si>
-  <si>
-    <t>Perform network diagnostics, test bandwidth utilization, verify switch and firewall configurations, monitor latency and packet loss, optimize network paths, and implement continuous monitoring</t>
-  </si>
-  <si>
-    <t>Network,ConferenceCall,VoIP,Teams,Bandwidth,Latency,PacketLoss,Troubleshooting</t>
-  </si>
-  <si>
-    <t>SDAP (Internal) - PDGM, MSP, Serious network problem for doing conference call, v20260708.eml</t>
-  </si>
-  <si>
-    <t>Suspicious Network Activity Detected by MDR</t>
-  </si>
-  <si>
-    <t>MDR platform detected abnormal network activity associated with a monitored endpoint, indicating possible unauthorized communication or compromise</t>
-  </si>
-  <si>
-    <t>Suspicious outbound or inbound network traffic triggered threat detection rules and required investigation to determine legitimacy and potential security impact</t>
-  </si>
-  <si>
-    <t>Review MDR alerts, investigate network connections, validate user activity, perform threat hunting, isolate affected endpoint if necessary, and implement remediation actions based on findings</t>
-  </si>
-  <si>
-    <t>MDR,NetworkActivity,SecurityIncident,ThreatHunting,EDR,Cybersecurity,Investigation</t>
-  </si>
-  <si>
-    <t>SDAP - OTEL, MSP, MDR Alert (Jackie Tsang, 10.255.70.57, Suspicious Network Activity), v20260706.eml</t>
-  </si>
-  <si>
-    <t>BBG-CN Disk Utilisation Alert</t>
-  </si>
-  <si>
-    <t>Server or workstation storage utilization exceeded predefined monitoring thresholds and may impact system performance or operations</t>
-  </si>
-  <si>
-    <t>Excessive disk consumption caused by large files, application data growth, log accumulation, backups, or insufficient storage allocation</t>
-  </si>
-  <si>
-    <t>Analyze disk usage, identify storage-consuming directories, remove unnecessary files, archive historical data, increase storage capacity if required, and implement storage monitoring</t>
-  </si>
-  <si>
-    <t>DiskUtilisation,Storage,Monitoring,RMM,Server,CapacityManagement,CloudAlpha</t>
-  </si>
-  <si>
-    <t>SDAP - CloudAlpha, MSP, Monitoring Alert (BBG-CN, BBG-CN_admin, Disk Utilisation), v20260706.eml</t>
-  </si>
-  <si>
     <t>Microsoft 365 Account Takeover and Internal Phishing Campaign</t>
   </si>
   <si>
+    <t>Multiple Microsoft 365 accounts were compromised and used to distribute phishing emails internally and externally</t>
+  </si>
+  <si>
+    <t>Phishing-based credential theft and session token theft enabled attackers to bypass MFA and gain unauthorized mailbox access</t>
+  </si>
+  <si>
+    <t>Reset passwords, revoke sessions and refresh tokens, enforce MFA re-registration, review mailbox rules, investigate OAuth permissions and improve phishing awareness training</t>
+  </si>
+  <si>
+    <t>Microsoft365,Phishing,AccountTakeover,MFA,TokenTheft,EmailSecurity</t>
+  </si>
+  <si>
+    <t>Incident Report</t>
+  </si>
+  <si>
     <t>KB011</t>
   </si>
   <si>
     <t>EVANLU-PC Critical Disk Utilisation Alert</t>
   </si>
   <si>
+    <t>Endpoint storage utilization exceeded alert threshold and generated repeated low disk space alerts</t>
+  </si>
+  <si>
+    <t>Excessive storage consumption caused by temporary files, caches, user files, downloads, archives or abnormal storage growth</t>
+  </si>
+  <si>
+    <t>Perform disk cleanup, remove temporary files, clear application cache, analyze large files, validate free space recovery and continue monitoring</t>
+  </si>
+  <si>
+    <t>DiskUtilisation,Storage,Monitoring,Windows,Endpoint,Cleanup</t>
+  </si>
+  <si>
     <t>KB012</t>
   </si>
   <si>
     <t>Microsoft Teams Conference Call Quality Degradation</t>
   </si>
   <si>
+    <t>Users experienced weak connection warnings, audio distortion, video freezing and poor Microsoft Teams meeting quality</t>
+  </si>
+  <si>
+    <t>Wireless network quality issues including weak signal strength, roaming events, packet loss, interference and access point performance degradation</t>
+  </si>
+  <si>
+    <t>Validate Wi-Fi connectivity, collect Teams diagnostics, review AP statistics, update wireless drivers, optimize Wi-Fi coverage and implement QoS controls</t>
+  </si>
+  <si>
+    <t>MicrosoftTeams,WiFi,PacketLoss,Network,ConferenceCall,VoIP,QoS</t>
+  </si>
+  <si>
+    <t>Troubleshooting Case</t>
+  </si>
+  <si>
     <t>KB013</t>
   </si>
   <si>
     <t>Potential Credential Access Activity on Endpoint T337</t>
   </si>
   <si>
+    <t>MDR detected credential access activity involving registry modifications and driver installations</t>
+  </si>
+  <si>
+    <t>EuMrx Network Provider changes triggered a credential access detection and required validation to determine if activity was authorised</t>
+  </si>
+  <si>
+    <t>Validate software installation, review logs, verify digital signatures, investigate administrator activity, isolate endpoint if necessary</t>
+  </si>
+  <si>
+    <t>MDR,CredentialAccess,NPPSpy,T1003,DattoEDR,ThreatHunting</t>
+  </si>
+  <si>
     <t>KB014</t>
   </si>
   <si>
@@ -305,6 +355,18 @@
     <t>Professionalism and Attendance Standards</t>
   </si>
   <si>
+    <t>Recurring lateness and inconsistent attendance may impact professionalism and team accountability</t>
+  </si>
+  <si>
+    <t>Lack of punctuality and attendance discipline can affect reliability, workplace culture and professional reputation</t>
+  </si>
+  <si>
+    <t>Reinforce attendance standards, promote accountability, monitor attendance trends and recognize professional behaviour</t>
+  </si>
+  <si>
+    <t>Attendance,Professionalism,Leadership,Management,WorkplaceCulture</t>
+  </si>
+  <si>
     <t>Internal Email</t>
   </si>
   <si>
@@ -317,72 +379,6 @@
     <t>LEAD8 External Cyber Risk Assessment</t>
   </si>
   <si>
-    <t>Multiple Microsoft 365 accounts were compromised and used to distribute phishing emails internally and externally</t>
-  </si>
-  <si>
-    <t>Phishing-based credential theft and session token theft enabled attackers to bypass MFA and gain unauthorized mailbox access</t>
-  </si>
-  <si>
-    <t>Reset passwords, revoke sessions and refresh tokens, enforce MFA re-registration, review mailbox rules, investigate OAuth permissions and improve phishing awareness training</t>
-  </si>
-  <si>
-    <t>Microsoft365,Phishing,AccountTakeover,MFA,TokenTheft,EmailSecurity</t>
-  </si>
-  <si>
-    <t>Incident Report</t>
-  </si>
-  <si>
-    <t>Endpoint storage utilization exceeded alert threshold and generated repeated low disk space alerts</t>
-  </si>
-  <si>
-    <t>Excessive storage consumption caused by temporary files, caches, user files, downloads, archives or abnormal storage growth</t>
-  </si>
-  <si>
-    <t>Perform disk cleanup, remove temporary files, clear application cache, analyze large files, validate free space recovery and continue monitoring</t>
-  </si>
-  <si>
-    <t>DiskUtilisation,Storage,Monitoring,Windows,Endpoint,Cleanup</t>
-  </si>
-  <si>
-    <t>Users experienced weak connection warnings, audio distortion, video freezing and poor Microsoft Teams meeting quality</t>
-  </si>
-  <si>
-    <t>Wireless network quality issues including weak signal strength, roaming events, packet loss, interference and access point performance degradation</t>
-  </si>
-  <si>
-    <t>Validate Wi-Fi connectivity, collect Teams diagnostics, review AP statistics, update wireless drivers, optimize Wi-Fi coverage and implement QoS controls</t>
-  </si>
-  <si>
-    <t>MicrosoftTeams,WiFi,PacketLoss,Network,ConferenceCall,VoIP,QoS</t>
-  </si>
-  <si>
-    <t>Troubleshooting Case</t>
-  </si>
-  <si>
-    <t>MDR detected credential access activity involving registry modifications and driver installations</t>
-  </si>
-  <si>
-    <t>EuMrx Network Provider changes triggered a credential access detection and required validation to determine if activity was authorised</t>
-  </si>
-  <si>
-    <t>Validate software installation, review logs, verify digital signatures, investigate administrator activity, isolate endpoint if necessary</t>
-  </si>
-  <si>
-    <t>MDR,CredentialAccess,NPPSpy,T1003,DattoEDR,ThreatHunting</t>
-  </si>
-  <si>
-    <t>Recurring lateness and inconsistent attendance may impact professionalism and team accountability</t>
-  </si>
-  <si>
-    <t>Lack of punctuality and attendance discipline can affect reliability, workplace culture and professional reputation</t>
-  </si>
-  <si>
-    <t>Reinforce attendance standards, promote accountability, monitor attendance trends and recognize professional behaviour</t>
-  </si>
-  <si>
-    <t>Attendance,Professionalism,Leadership,Management,WorkplaceCulture</t>
-  </si>
-  <si>
     <t>External cyber risk assessment identified credential exposure, phishing risk and web security weaknesses</t>
   </si>
   <si>
@@ -530,6 +526,9 @@
     <t>Teams,ISP,Latency,PacketLoss,Collaboration,RCA</t>
   </si>
   <si>
+    <t>KB023</t>
+  </si>
+  <si>
     <t>Exchange Online Mail Flow Interruption</t>
   </si>
   <si>
@@ -545,6 +544,9 @@
     <t>ExchangeOnline,MailFlow,Email,SpamFilter,Microsoft365</t>
   </si>
   <si>
+    <t>KB024</t>
+  </si>
+  <si>
     <t>MFA Enrollment Failure</t>
   </si>
   <si>
@@ -560,6 +562,9 @@
     <t>Microsoft365,MFA,ConditionalAccess,Authenticator,EntraID</t>
   </si>
   <si>
+    <t>KB025</t>
+  </si>
+  <si>
     <t>Outlook OST File Corruption</t>
   </si>
   <si>
@@ -575,6 +580,9 @@
     <t>Outlook,OST,Synchronization,Profile,Email</t>
   </si>
   <si>
+    <t>KB026</t>
+  </si>
+  <si>
     <t>Shared Mailbox Permission Issue</t>
   </si>
   <si>
@@ -590,6 +598,9 @@
     <t>SharedMailbox,ExchangeOnline,Permissions,Microsoft365</t>
   </si>
   <si>
+    <t>KB027</t>
+  </si>
+  <si>
     <t>Microsoft Teams Login Failure</t>
   </si>
   <si>
@@ -605,6 +616,9 @@
     <t>Teams,Authentication,Login,Token,Microsoft365</t>
   </si>
   <si>
+    <t>KB028</t>
+  </si>
+  <si>
     <t>OneDrive Synchronization Conflict</t>
   </si>
   <si>
@@ -620,7 +634,7 @@
     <t>OneDrive,Sync,CloudStorage,Files,Microsoft365</t>
   </si>
   <si>
-    <t>KB023</t>
+    <t>KB029</t>
   </si>
   <si>
     <t>Email Quarantine False Positive</t>
@@ -638,7 +652,7 @@
     <t>Defender,Quarantine,EmailSecurity,Microsoft365</t>
   </si>
   <si>
-    <t>KB024</t>
+    <t>KB030</t>
   </si>
   <si>
     <t>Mailbox Storage Quota Reached</t>
@@ -656,7 +670,7 @@
     <t>ExchangeOnline,MailboxQuota,Storage,Email</t>
   </si>
   <si>
-    <t>KB025</t>
+    <t>KB031</t>
   </si>
   <si>
     <t>Conditional Access Blocking Login</t>
@@ -674,7 +688,7 @@
     <t>ConditionalAccess,AzureAD,EntraID,Microsoft365</t>
   </si>
   <si>
-    <t>KB026</t>
+    <t>KB032</t>
   </si>
   <si>
     <t>Azure AD Connect Synchronization Failure</t>
@@ -692,7 +706,7 @@
     <t>AzureADConnect,EntraID,Synchronization,ActiveDirectory</t>
   </si>
   <si>
-    <t>KB027</t>
+    <t>KB033</t>
   </si>
   <si>
     <t>SharePoint External Sharing Disabled</t>
@@ -710,7 +724,7 @@
     <t>SharePoint,ExternalSharing,Collaboration,Microsoft365</t>
   </si>
   <si>
-    <t>KB028</t>
+    <t>KB034</t>
   </si>
   <si>
     <t>Missing Teams Meeting Recording</t>
@@ -728,7 +742,7 @@
     <t>Teams,Recording,OneDrive,Meetings,Microsoft365</t>
   </si>
   <si>
-    <t>KB029</t>
+    <t>KB035</t>
   </si>
   <si>
     <t>Suspicious Mail Forwarding Rule Detected</t>
@@ -746,7 +760,7 @@
     <t>MailForwarding,Compromise,EmailSecurity,Microsoft365</t>
   </si>
   <si>
-    <t>KB030</t>
+    <t>KB036</t>
   </si>
   <si>
     <t>Autodiscover Configuration Failure</t>
@@ -764,22 +778,7 @@
     <t>Autodiscover,DNS,Outlook,ExchangeOnline,Microsoft365</t>
   </si>
   <si>
-    <t>KB031</t>
-  </si>
-  <si>
-    <t>KB032</t>
-  </si>
-  <si>
-    <t>KB033</t>
-  </si>
-  <si>
-    <t>KB034</t>
-  </si>
-  <si>
-    <t>KB035</t>
-  </si>
-  <si>
-    <t>KB036</t>
+    <t>KB037</t>
   </si>
   <si>
     <t>Finance staff received fraudulent payment instructions appearing to originate from senior management</t>
@@ -794,6 +793,9 @@
     <t>BEC,EmailSecurity,Spoofing,Finance,Phishing</t>
   </si>
   <si>
+    <t>KB038</t>
+  </si>
+  <si>
     <t>Credential Stuffing Attack Detected</t>
   </si>
   <si>
@@ -812,6 +814,9 @@
     <t>Security Alert</t>
   </si>
   <si>
+    <t>KB039</t>
+  </si>
+  <si>
     <t>Impossible Travel Login Alert</t>
   </si>
   <si>
@@ -827,6 +832,9 @@
     <t>ImpossibleTravel,EntraID,Microsoft365,IdentitySecurity</t>
   </si>
   <si>
+    <t>KB040</t>
+  </si>
+  <si>
     <t>MFA Fatigue Attack</t>
   </si>
   <si>
@@ -842,6 +850,9 @@
     <t>MFAFatigue,MFA,AccountCompromise,IdentitySecurity</t>
   </si>
   <si>
+    <t>KB041</t>
+  </si>
+  <si>
     <t>Malicious PowerShell Activity Detected</t>
   </si>
   <si>
@@ -860,6 +871,9 @@
     <t>MDR Alert</t>
   </si>
   <si>
+    <t>KB042</t>
+  </si>
+  <si>
     <t>Suspicious Remote Desktop Activity</t>
   </si>
   <si>
@@ -875,7 +889,7 @@
     <t>RDP,RemoteAccess,BruteForce,Security</t>
   </si>
   <si>
-    <t>KB037</t>
+    <t>KB043</t>
   </si>
   <si>
     <t>Malware Infection on Workstation</t>
@@ -893,7 +907,7 @@
     <t>Malware,EndpointSecurity,Antivirus,Cybersecurity</t>
   </si>
   <si>
-    <t>KB038</t>
+    <t>KB044</t>
   </si>
   <si>
     <t>Unauthorized VPN Access Attempt</t>
@@ -911,7 +925,7 @@
     <t>VPN,IdentitySecurity,UnauthorizedAccess</t>
   </si>
   <si>
-    <t>KB039</t>
+    <t>KB045</t>
   </si>
   <si>
     <t>DNS Tunneling Detection</t>
@@ -929,7 +943,7 @@
     <t>DNSTunneling,DNS,C2,ThreatHunting</t>
   </si>
   <si>
-    <t>KB040</t>
+    <t>KB046</t>
   </si>
   <si>
     <t>User Clicked Phishing Link</t>
@@ -947,7 +961,7 @@
     <t>Phishing,EmailSecurity,UserAwareness</t>
   </si>
   <si>
-    <t>KB041</t>
+    <t>KB047</t>
   </si>
   <si>
     <t>Session Token Theft Suspicion</t>
@@ -965,7 +979,7 @@
     <t>TokenTheft,SessionHijacking,IdentitySecurity</t>
   </si>
   <si>
-    <t>KB042</t>
+    <t>KB048</t>
   </si>
   <si>
     <t>Unauthorized OAuth Application Consent</t>
@@ -983,7 +997,7 @@
     <t>OAuth,CloudSecurity,Microsoft365,Permissions</t>
   </si>
   <si>
-    <t>KB043</t>
+    <t>KB049</t>
   </si>
   <si>
     <t>Endpoint Protection Disabled</t>
@@ -1001,7 +1015,7 @@
     <t>Antivirus,EndpointSecurity,Compliance</t>
   </si>
   <si>
-    <t>KB044</t>
+    <t>KB050</t>
   </si>
   <si>
     <t>Early Ransomware Activity Detected</t>
@@ -1019,7 +1033,7 @@
     <t>Ransomware,Encryption,EDR,IncidentResponse</t>
   </si>
   <si>
-    <t>KB045</t>
+    <t>KB051</t>
   </si>
   <si>
     <t>Privileged Account Misuse</t>
@@ -1037,22 +1051,7 @@
     <t>PrivilegedAccess,AdminAccount,Audit,IdentitySecurity</t>
   </si>
   <si>
-    <t>KB046</t>
-  </si>
-  <si>
-    <t>KB047</t>
-  </si>
-  <si>
-    <t>KB048</t>
-  </si>
-  <si>
-    <t>KB049</t>
-  </si>
-  <si>
-    <t>KB050</t>
-  </si>
-  <si>
-    <t>KB051</t>
+    <t>KB052</t>
   </si>
   <si>
     <t>Critical Disk Utilisation Alert</t>
@@ -1070,6 +1069,9 @@
     <t>DiskUtilisation,Storage,Capacity,Monitoring</t>
   </si>
   <si>
+    <t>KB053</t>
+  </si>
+  <si>
     <t>High CPU Utilisation Alert</t>
   </si>
   <si>
@@ -1085,6 +1087,9 @@
     <t>CPU,Performance,ResourceUtilisation,Monitoring</t>
   </si>
   <si>
+    <t>KB054</t>
+  </si>
+  <si>
     <t>High Memory Consumption Alert</t>
   </si>
   <si>
@@ -1100,6 +1105,9 @@
     <t>Memory,RAM,Performance,Monitoring</t>
   </si>
   <si>
+    <t>KB055</t>
+  </si>
+  <si>
     <t>Critical Windows Service Stopped</t>
   </si>
   <si>
@@ -1115,6 +1123,9 @@
     <t>WindowsService,SystemFailure,Troubleshooting</t>
   </si>
   <si>
+    <t>KB056</t>
+  </si>
+  <si>
     <t>Daily Backup Failure Alert</t>
   </si>
   <si>
@@ -1130,6 +1141,9 @@
     <t>Backup,DisasterRecovery,Storage,Monitoring</t>
   </si>
   <si>
+    <t>KB057</t>
+  </si>
+  <si>
     <t>SQL Database Growth Alert</t>
   </si>
   <si>
@@ -1145,7 +1159,7 @@
     <t>SQL,Database,Storage,Capacity</t>
   </si>
   <si>
-    <t>KB052</t>
+    <t>KB058</t>
   </si>
   <si>
     <t>IIS Service Outage Alert</t>
@@ -1163,7 +1177,7 @@
     <t>IIS,WebServer,Website,Monitoring</t>
   </si>
   <si>
-    <t>KB053</t>
+    <t>KB059</t>
   </si>
   <si>
     <t>Active Directory Replication Failure</t>
@@ -1181,7 +1195,7 @@
     <t>ActiveDirectory,Replication,DNS,DomainController</t>
   </si>
   <si>
-    <t>KB054</t>
+    <t>KB060</t>
   </si>
   <si>
     <t>High Network Utilisation Alert</t>
@@ -1199,7 +1213,7 @@
     <t>Network,Bandwidth,QoS,Performance</t>
   </si>
   <si>
-    <t>KB055</t>
+    <t>KB061</t>
   </si>
   <si>
     <t>Print Server Service Failure</t>
@@ -1217,7 +1231,7 @@
     <t>PrintServer,Spooler,Printer,Troubleshooting</t>
   </si>
   <si>
-    <t>KB056</t>
+    <t>KB062</t>
   </si>
   <si>
     <t>DHCP Scope Exhaustion Alert</t>
@@ -1235,7 +1249,7 @@
     <t>DHCP,IPAddress,Network,Infrastructure</t>
   </si>
   <si>
-    <t>KB057</t>
+    <t>KB063</t>
   </si>
   <si>
     <t>DNS Service Availability Alert</t>
@@ -1253,7 +1267,7 @@
     <t>DNS,NameResolution,Network,Troubleshooting</t>
   </si>
   <si>
-    <t>KB058</t>
+    <t>KB064</t>
   </si>
   <si>
     <t>Hyper-V Host Resource Exhaustion</t>
@@ -1271,7 +1285,7 @@
     <t>HyperV,Virtualization,Performance,Infrastructure</t>
   </si>
   <si>
-    <t>KB059</t>
+    <t>KB065</t>
   </si>
   <si>
     <t>VMware Datastore Capacity Warning</t>
@@ -1289,7 +1303,7 @@
     <t>VMware,Datastore,Virtualization,Storage</t>
   </si>
   <si>
-    <t>KB060</t>
+    <t>KB066</t>
   </si>
   <si>
     <t>SSL Certificate Expiry Alert</t>
@@ -1307,22 +1321,7 @@
     <t>SSL,TLS,Certificate,Security,Monitoring</t>
   </si>
   <si>
-    <t>KB061</t>
-  </si>
-  <si>
-    <t>KB062</t>
-  </si>
-  <si>
-    <t>KB063</t>
-  </si>
-  <si>
-    <t>KB064</t>
-  </si>
-  <si>
-    <t>KB065</t>
-  </si>
-  <si>
-    <t>KB066</t>
+    <t>KB067</t>
   </si>
   <si>
     <t>VPN Service Outage During Business Hours</t>
@@ -1340,6 +1339,9 @@
     <t>VPN,SSL,Certificate,RemoteAccess,RCA</t>
   </si>
   <si>
+    <t>KB068</t>
+  </si>
+  <si>
     <t>Wi-Fi Roaming Performance Issue</t>
   </si>
   <si>
@@ -1355,6 +1357,9 @@
     <t>WiFi,Roaming,Wireless,Network,RCA</t>
   </si>
   <si>
+    <t>KB069</t>
+  </si>
+  <si>
     <t>Microsoft Teams Audio Quality Degradation</t>
   </si>
   <si>
@@ -1370,6 +1375,9 @@
     <t>Teams,VoIP,PacketLoss,QoS,Network,RCA</t>
   </si>
   <si>
+    <t>KB070</t>
+  </si>
+  <si>
     <t>NAS Storage Capacity Exhaustion</t>
   </si>
   <si>
@@ -1385,6 +1393,9 @@
     <t>NAS,Storage,FileServer,Capacity,RCA</t>
   </si>
   <si>
+    <t>KB071</t>
+  </si>
+  <si>
     <t>SharePoint Synchronization Failure</t>
   </si>
   <si>
@@ -1400,6 +1411,9 @@
     <t>SharePoint,OneDrive,CloudStorage,Sync,RCA</t>
   </si>
   <si>
+    <t>KB072</t>
+  </si>
+  <si>
     <t>Firewall Firmware Upgrade Failure</t>
   </si>
   <si>
@@ -1415,7 +1429,7 @@
     <t>Firewall,Firmware,Network,Internet,RCA</t>
   </si>
   <si>
-    <t>KB067</t>
+    <t>KB073</t>
   </si>
   <si>
     <t>Backup Corruption Incident</t>
@@ -1433,7 +1447,7 @@
     <t>Backup,Restore,DisasterRecovery,Storage,RCA</t>
   </si>
   <si>
-    <t>KB068</t>
+    <t>KB074</t>
   </si>
   <si>
     <t>Windows Update Deployment Failure</t>
@@ -1451,7 +1465,7 @@
     <t>WindowsUpdate,Patching,Endpoint,RCA</t>
   </si>
   <si>
-    <t>KB069</t>
+    <t>KB075</t>
   </si>
   <si>
     <t>File Server Performance Degradation</t>
@@ -1469,7 +1483,7 @@
     <t>FileServer,DiskIO,Performance,Storage,RCA</t>
   </si>
   <si>
-    <t>KB070</t>
+    <t>KB076</t>
   </si>
   <si>
     <t>DNS Resolution Latency</t>
@@ -1487,7 +1501,7 @@
     <t>DNS,Latency,NameResolution,Network,RCA</t>
   </si>
   <si>
-    <t>KB071</t>
+    <t>KB077</t>
   </si>
   <si>
     <t>Active Directory Authentication Failure</t>
@@ -1505,7 +1519,7 @@
     <t>ActiveDirectory,Authentication,DomainController,RCA</t>
   </si>
   <si>
-    <t>KB072</t>
+    <t>KB078</t>
   </si>
   <si>
     <t>Exchange Hybrid Connectivity Issue</t>
@@ -1523,7 +1537,7 @@
     <t>ExchangeHybrid,MailFlow,Microsoft365,RCA</t>
   </si>
   <si>
-    <t>KB073</t>
+    <t>KB079</t>
   </si>
   <si>
     <t>Network Loop Causing Broadcast Storm</t>
@@ -1541,7 +1555,7 @@
     <t>NetworkLoop,Switch,STP,BroadcastStorm,RCA</t>
   </si>
   <si>
-    <t>KB074</t>
+    <t>KB080</t>
   </si>
   <si>
     <t>Endpoint Security Agent Instability</t>
@@ -1559,7 +1573,7 @@
     <t>EndpointSecurity,Antivirus,Performance,RCA</t>
   </si>
   <si>
-    <t>KB075</t>
+    <t>KB081</t>
   </si>
   <si>
     <t>Disk I/O Bottleneck on Virtual Host</t>
@@ -1577,7 +1591,7 @@
     <t>Virtualization,DiskIO,Performance,Storage,RCA</t>
   </si>
   <si>
-    <t>KB076</t>
+    <t>KB082</t>
   </si>
   <si>
     <t>SQL Service Performance Degradation</t>
@@ -1595,7 +1609,7 @@
     <t>SQL,Database,Performance,Application,RCA</t>
   </si>
   <si>
-    <t>KB077</t>
+    <t>KB083</t>
   </si>
   <si>
     <t>Conditional Access Policy Misconfiguration</t>
@@ -1613,7 +1627,7 @@
     <t>ConditionalAccess,EntraID,Microsoft365,RCA</t>
   </si>
   <si>
-    <t>KB078</t>
+    <t>KB084</t>
   </si>
   <si>
     <t>Certificate Trust Chain Failure</t>
@@ -1631,7 +1645,7 @@
     <t>Certificate,PKI,SSL,TLS,RCA</t>
   </si>
   <si>
-    <t>KB079</t>
+    <t>KB085</t>
   </si>
   <si>
     <t>ISP Routing Instability</t>
@@ -1649,7 +1663,7 @@
     <t>ISP,Routing,PacketLoss,Connectivity,RCA</t>
   </si>
   <si>
-    <t>KB080</t>
+    <t>KB086</t>
   </si>
   <si>
     <t>Storage Controller Failure</t>
@@ -1667,22 +1681,7 @@
     <t>Storage,Controller,HardwareFailure,SAN,RCA</t>
   </si>
   <si>
-    <t>KB081</t>
-  </si>
-  <si>
-    <t>KB082</t>
-  </si>
-  <si>
-    <t>KB083</t>
-  </si>
-  <si>
-    <t>KB084</t>
-  </si>
-  <si>
-    <t>KB085</t>
-  </si>
-  <si>
-    <t>KB086</t>
+    <t>KB087</t>
   </si>
   <si>
     <t>SOP Procedure</t>
@@ -1706,6 +1705,9 @@
     <t>SOP</t>
   </si>
   <si>
+    <t>KB088</t>
+  </si>
+  <si>
     <t>Employee Offboarding Procedure</t>
   </si>
   <si>
@@ -1721,6 +1723,9 @@
     <t>Offboarding,AccountTermination,Security</t>
   </si>
   <si>
+    <t>KB089</t>
+  </si>
+  <si>
     <t>Microsoft 365 Password Reset Procedure</t>
   </si>
   <si>
@@ -1736,6 +1741,9 @@
     <t>Microsoft365,PasswordReset,Authentication</t>
   </si>
   <si>
+    <t>KB090</t>
+  </si>
+  <si>
     <t>Multi-Factor Authentication Reset Procedure</t>
   </si>
   <si>
@@ -1751,6 +1759,9 @@
     <t>MFA,Microsoft365,Security</t>
   </si>
   <si>
+    <t>KB091</t>
+  </si>
+  <si>
     <t>VPN User Setup Procedure</t>
   </si>
   <si>
@@ -1766,6 +1777,9 @@
     <t>VPN,RemoteAccess,Firewall</t>
   </si>
   <si>
+    <t>KB092</t>
+  </si>
+  <si>
     <t>Corporate Laptop Deployment Procedure</t>
   </si>
   <si>
@@ -1781,7 +1795,7 @@
     <t>LaptopDeployment,Windows,Endpoint</t>
   </si>
   <si>
-    <t>KB087</t>
+    <t>KB093</t>
   </si>
   <si>
     <t>Network Printer Installation Procedure</t>
@@ -1799,7 +1813,7 @@
     <t>Printer,Driver,NetworkPrinting</t>
   </si>
   <si>
-    <t>KB088</t>
+    <t>KB094</t>
   </si>
   <si>
     <t>BitLocker Recovery Key Procedure</t>
@@ -1817,7 +1831,7 @@
     <t>BitLocker,Encryption,Recovery</t>
   </si>
   <si>
-    <t>KB089</t>
+    <t>KB095</t>
   </si>
   <si>
     <t>Microsoft Teams User Setup Procedure</t>
@@ -1835,7 +1849,7 @@
     <t>Teams,Microsoft365,Collaboration</t>
   </si>
   <si>
-    <t>KB090</t>
+    <t>KB096</t>
   </si>
   <si>
     <t>Shared Mailbox Creation Procedure</t>
@@ -1853,7 +1867,7 @@
     <t>SharedMailbox,ExchangeOnline,Microsoft365</t>
   </si>
   <si>
-    <t>KB091</t>
+    <t>KB097</t>
   </si>
   <si>
     <t>Security Incident Escalation Procedure</t>
@@ -1871,7 +1885,7 @@
     <t>SecurityIncident,Escalation,Cybersecurity</t>
   </si>
   <si>
-    <t>KB092</t>
+    <t>KB098</t>
   </si>
   <si>
     <t>Backup Verification Procedure</t>
@@ -1889,7 +1903,7 @@
     <t>Backup,Restore,Validation</t>
   </si>
   <si>
-    <t>KB093</t>
+    <t>KB099</t>
   </si>
   <si>
     <t>Monthly Patch Management Procedure</t>
@@ -1907,7 +1921,7 @@
     <t>Patching,WindowsUpdate,Security</t>
   </si>
   <si>
-    <t>KB094</t>
+    <t>KB100</t>
   </si>
   <si>
     <t>Firewall Rule Change Procedure</t>
@@ -1925,7 +1939,7 @@
     <t>Firewall,NetworkSecurity,ChangeManagement</t>
   </si>
   <si>
-    <t>KB095</t>
+    <t>KB101</t>
   </si>
   <si>
     <t>Device Enrollment Procedure</t>
@@ -1943,7 +1957,7 @@
     <t>Endpoint,RMM,Enrollment</t>
   </si>
   <si>
-    <t>KB096</t>
+    <t>KB102</t>
   </si>
   <si>
     <t>Disk Cleanup Procedure</t>
@@ -1961,7 +1975,7 @@
     <t>DiskCleanup,Storage,Windows</t>
   </si>
   <si>
-    <t>KB097</t>
+    <t>KB103</t>
   </si>
   <si>
     <t>Phishing Incident Response Procedure</t>
@@ -1979,7 +1993,7 @@
     <t>Phishing,EmailSecurity,IncidentResponse</t>
   </si>
   <si>
-    <t>KB098</t>
+    <t>KB104</t>
   </si>
   <si>
     <t>Malware Containment Procedure</t>
@@ -1997,7 +2011,7 @@
     <t>Malware,Containment,EndpointSecurity</t>
   </si>
   <si>
-    <t>KB099</t>
+    <t>KB105</t>
   </si>
   <si>
     <t>SSL Certificate Renewal Procedure</t>
@@ -2015,7 +2029,7 @@
     <t>SSL,TLS,Certificate,Security</t>
   </si>
   <si>
-    <t>KB100</t>
+    <t>KB106</t>
   </si>
   <si>
     <t>Ticket Closure Validation Procedure</t>
@@ -2033,22 +2047,7 @@
     <t>TicketManagement,ServiceDesk,SLA</t>
   </si>
   <si>
-    <t>KB101</t>
-  </si>
-  <si>
-    <t>KB102</t>
-  </si>
-  <si>
-    <t>KB103</t>
-  </si>
-  <si>
-    <t>KB104</t>
-  </si>
-  <si>
-    <t>KB105</t>
-  </si>
-  <si>
-    <t>KB106</t>
+    <t>KB107</t>
   </si>
   <si>
     <t>Microsoft 365 License Assignment Procedure</t>
@@ -2066,6 +2065,9 @@
     <t>Microsoft365,License,UserManagement</t>
   </si>
   <si>
+    <t>KB108</t>
+  </si>
+  <si>
     <t>Microsoft 365 User Account Creation Procedure</t>
   </si>
   <si>
@@ -2081,6 +2083,9 @@
     <t>Microsoft365,UserProvisioning,EntraID</t>
   </si>
   <si>
+    <t>KB109</t>
+  </si>
+  <si>
     <t>Shared Drive Access Request Procedure</t>
   </si>
   <si>
@@ -2096,6 +2101,9 @@
     <t>FileServer,Permissions,AccessControl</t>
   </si>
   <si>
+    <t>KB110</t>
+  </si>
+  <si>
     <t>File Restore from Backup Procedure</t>
   </si>
   <si>
@@ -2111,6 +2119,9 @@
     <t>Backup,Restore,Recovery</t>
   </si>
   <si>
+    <t>KB111</t>
+  </si>
+  <si>
     <t>Windows Local Administrator Reset Procedure</t>
   </si>
   <si>
@@ -2126,6 +2137,9 @@
     <t>Windows,Administrator,Password</t>
   </si>
   <si>
+    <t>KB112</t>
+  </si>
+  <si>
     <t>Endpoint Antivirus Deployment Procedure</t>
   </si>
   <si>
@@ -2141,7 +2155,7 @@
     <t>Antivirus,EndpointSecurity,Deployment</t>
   </si>
   <si>
-    <t>KB107</t>
+    <t>KB113</t>
   </si>
   <si>
     <t>Microsoft Defender Alert Investigation Procedure</t>
@@ -2159,7 +2173,7 @@
     <t>Defender,SecurityAlert,ThreatHunting</t>
   </si>
   <si>
-    <t>KB108</t>
+    <t>KB114</t>
   </si>
   <si>
     <t>New Mobile Device Enrollment Procedure</t>
@@ -2177,7 +2191,7 @@
     <t>MobileDevice,MDM,Enrollment</t>
   </si>
   <si>
-    <t>KB109</t>
+    <t>KB115</t>
   </si>
   <si>
     <t>Corporate Email Signature Deployment Procedure</t>
@@ -2195,7 +2209,7 @@
     <t>Email,Signature,Outlook</t>
   </si>
   <si>
-    <t>KB110</t>
+    <t>KB116</t>
   </si>
   <si>
     <t>Microsoft Teams Team Creation Procedure</t>
@@ -2213,7 +2227,7 @@
     <t>Teams,Collaboration,Microsoft365</t>
   </si>
   <si>
-    <t>KB111</t>
+    <t>KB117</t>
   </si>
   <si>
     <t>User Access Review Procedure</t>
@@ -2231,7 +2245,7 @@
     <t>AccessReview,Permissions,Compliance</t>
   </si>
   <si>
-    <t>KB112</t>
+    <t>KB118</t>
   </si>
   <si>
     <t>Security Awareness Training Enrollment Procedure</t>
@@ -2249,7 +2263,7 @@
     <t>SAT,Training,Cybersecurity</t>
   </si>
   <si>
-    <t>KB113</t>
+    <t>KB119</t>
   </si>
   <si>
     <t>Domain Password Policy Configuration Procedure</t>
@@ -2267,7 +2281,7 @@
     <t>ActiveDirectory,PasswordPolicy,Security</t>
   </si>
   <si>
-    <t>KB114</t>
+    <t>KB120</t>
   </si>
   <si>
     <t>Workstation Replacement Procedure</t>
@@ -2285,7 +2299,7 @@
     <t>Endpoint,Lifecycle,Migration</t>
   </si>
   <si>
-    <t>KB115</t>
+    <t>KB121</t>
   </si>
   <si>
     <t>Windows Device Domain Join Procedure</t>
@@ -2303,7 +2317,7 @@
     <t>ActiveDirectory,DomainJoin,Windows</t>
   </si>
   <si>
-    <t>KB116</t>
+    <t>KB122</t>
   </si>
   <si>
     <t>Remote Support Session Procedure</t>
@@ -2321,7 +2335,7 @@
     <t>RemoteSupport,Helpdesk,Troubleshooting</t>
   </si>
   <si>
-    <t>KB117</t>
+    <t>KB123</t>
   </si>
   <si>
     <t>Email Distribution Group Creation Procedure</t>
@@ -2339,7 +2353,7 @@
     <t>ExchangeOnline,DistributionGroup,Email</t>
   </si>
   <si>
-    <t>KB118</t>
+    <t>KB124</t>
   </si>
   <si>
     <t>New Shared Folder Provisioning Procedure</t>
@@ -2357,7 +2371,7 @@
     <t>FileServer,SharedFolder,Permissions</t>
   </si>
   <si>
-    <t>KB119</t>
+    <t>KB125</t>
   </si>
   <si>
     <t>DNS Record Modification Procedure</t>
@@ -2375,7 +2389,7 @@
     <t>DNS,Networking,Infrastructure</t>
   </si>
   <si>
-    <t>KB120</t>
+    <t>KB126</t>
   </si>
   <si>
     <t>Wireless Access Point Deployment Procedure</t>
@@ -2393,7 +2407,7 @@
     <t>Wireless,WiFi,Networking</t>
   </si>
   <si>
-    <t>KB121</t>
+    <t>KB127</t>
   </si>
   <si>
     <t>SSL Certificate Installation Procedure</t>
@@ -2411,7 +2425,7 @@
     <t>SSL,TLS,Certificate</t>
   </si>
   <si>
-    <t>KB122</t>
+    <t>KB128</t>
   </si>
   <si>
     <t>Firewall Policy Review Procedure</t>
@@ -2429,7 +2443,7 @@
     <t>Firewall,Review,Security</t>
   </si>
   <si>
-    <t>KB123</t>
+    <t>KB129</t>
   </si>
   <si>
     <t>Microsoft 365 Mailbox Migration Procedure</t>
@@ -2447,7 +2461,7 @@
     <t>ExchangeOnline,Migration,Email</t>
   </si>
   <si>
-    <t>KB124</t>
+    <t>KB130</t>
   </si>
   <si>
     <t>Endpoint Compliance Verification Procedure</t>
@@ -2465,7 +2479,7 @@
     <t>Compliance,Endpoint,Security</t>
   </si>
   <si>
-    <t>KB125</t>
+    <t>KB131</t>
   </si>
   <si>
     <t>Network Switch Configuration Backup Procedure</t>
@@ -2483,7 +2497,7 @@
     <t>Network,Switch,Backup</t>
   </si>
   <si>
-    <t>KB126</t>
+    <t>KB132</t>
   </si>
   <si>
     <t>ISP Outage Escalation Procedure</t>
@@ -2501,7 +2515,7 @@
     <t>ISP,Internet,Escalation</t>
   </si>
   <si>
-    <t>KB127</t>
+    <t>KB133</t>
   </si>
   <si>
     <t>Microsoft 365 Guest User Provisioning Procedure</t>
@@ -2519,7 +2533,7 @@
     <t>GuestAccess,Microsoft365,Collaboration</t>
   </si>
   <si>
-    <t>KB128</t>
+    <t>KB134</t>
   </si>
   <si>
     <t>Server Reboot Change Procedure</t>
@@ -2537,7 +2551,7 @@
     <t>Server,Maintenance,ChangeManagement</t>
   </si>
   <si>
-    <t>KB129</t>
+    <t>KB135</t>
   </si>
   <si>
     <t>Vulnerability Remediation Procedure</t>
@@ -2555,7 +2569,7 @@
     <t>Vulnerability,Remediation,Security</t>
   </si>
   <si>
-    <t>KB130</t>
+    <t>KB136</t>
   </si>
   <si>
     <t>Disaster Recovery Validation Procedure</t>
@@ -2571,56 +2585,34 @@
   </si>
   <si>
     <t>DisasterRecovery,Backup,Testing</t>
-  </si>
-  <si>
-    <t>KB131</t>
-  </si>
-  <si>
-    <t>KB132</t>
-  </si>
-  <si>
-    <t>KB133</t>
-  </si>
-  <si>
-    <t>KB134</t>
-  </si>
-  <si>
-    <t>KB135</t>
-  </si>
-  <si>
-    <t>KB136</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <i val="0"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2633,7 +2625,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F5F5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2661,32 +2652,47 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2732,7 +2738,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2784,7 +2790,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2845,180 +2851,185 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702F8E0C-5333-48D4-BC8B-1F103EAD19F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{96DC6089-C456-4EAF-9F3F-D9F08B5BBAD5}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:I140"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.497499999999997" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="17.81640625" customWidth="1"/>
-    <col min="4" max="4" width="41.81640625" customWidth="1"/>
-    <col min="5" max="5" width="59.54296875" customWidth="1"/>
-    <col min="6" max="6" width="71.08984375" customWidth="1"/>
-    <col min="7" max="7" width="37.26953125" customWidth="1"/>
-    <col min="8" max="8" width="42.81640625" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.8515625" customWidth="1"/>
+    <col min="4" max="4" width="52.8515625" customWidth="1"/>
+    <col min="5" max="5" width="61.28125" customWidth="1"/>
+    <col min="6" max="6" width="64.28125" customWidth="1"/>
+    <col min="7" max="7" width="63.00390625" customWidth="1"/>
+    <col min="8" max="8" width="42.8515625" customWidth="1"/>
+    <col min="9" max="9" width="15.28125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3047,7 +3058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" ht="33.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -3076,7 +3087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" ht="50.25" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3105,7 +3116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" ht="33.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -3134,7 +3145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" ht="50.25" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -3142,48 +3153,48 @@
         <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" ht="33.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
@@ -3192,212 +3203,212 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" ht="50.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="66.75" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="66.75" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="66.75" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="I10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" ht="66.75" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="66.75" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="66.75" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="83.25" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="83" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>19</v>
@@ -3406,103 +3417,103 @@
         <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" ht="50.25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="66.75" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="I16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="66.75" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>16</v>
@@ -3511,44 +3522,44 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" ht="66.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="I18" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="66.75" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>114</v>
@@ -3569,7 +3580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" ht="66.75" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>119</v>
       </c>
@@ -3598,7 +3609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" ht="33.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
@@ -3627,7 +3638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" ht="50.25" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>133</v>
       </c>
@@ -3656,7 +3667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" ht="50.25" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>139</v>
       </c>
@@ -3685,7 +3696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" ht="50.25" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>145</v>
       </c>
@@ -3714,7 +3725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" ht="50.25" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>151</v>
       </c>
@@ -3737,13 +3748,13 @@
         <v>156</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" ht="66.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>157</v>
       </c>
@@ -3772,27 +3783,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" ht="50.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>26</v>
@@ -3801,27 +3812,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" ht="33.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>26</v>
@@ -3830,27 +3841,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" ht="33.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>26</v>
@@ -3859,172 +3870,172 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" ht="33.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" ht="33.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" ht="50.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" ht="33.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" ht="33.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" ht="33.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>26</v>
@@ -4033,114 +4044,114 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" ht="50.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" ht="50.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" ht="50.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" ht="50.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>19</v>
@@ -4149,27 +4160,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" ht="50.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>26</v>
@@ -4178,9 +4189,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" ht="50.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>19</v>
@@ -4189,886 +4200,886 @@
         <v>152</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" ht="33.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" ht="50.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="I43" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" ht="33.75" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" ht="50.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" ht="33.75" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" ht="33.75" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" ht="33.75" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" ht="33.75" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" ht="33.75" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" ht="33.75" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" ht="50.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" ht="50.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" ht="33.75" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" ht="33.75" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" ht="33.75" customHeight="1">
       <c r="A56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" ht="33.75" customHeight="1">
+      <c r="A57" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" ht="33.75" customHeight="1">
+      <c r="A58" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" ht="33.75" customHeight="1">
+      <c r="A59" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" ht="33.75" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" ht="33.75" customHeight="1">
+      <c r="A61" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="2" t="s">
+      <c r="B61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" ht="33.75" customHeight="1">
+      <c r="A62" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="2" t="s">
+      <c r="B62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" ht="33.75" customHeight="1">
+      <c r="A63" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" ht="33.75" customHeight="1">
+      <c r="A64" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="2" t="s">
+      <c r="B64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" ht="33.75" customHeight="1">
+      <c r="A65" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="2" t="s">
+      <c r="B65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" ht="33.75" customHeight="1">
+      <c r="A66" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="2" t="s">
+      <c r="B66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" ht="33.75" customHeight="1">
+      <c r="A67" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="2" t="s">
+      <c r="B67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" ht="50.25" customHeight="1">
+      <c r="A68" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="2" t="s">
+      <c r="B68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" ht="33.75" customHeight="1">
+      <c r="A69" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="2" t="s">
+      <c r="B69" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" ht="33.75" customHeight="1">
+      <c r="A70" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="2" t="s">
+      <c r="B70" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>421</v>
-      </c>
       <c r="H70" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" ht="50.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>458</v>
+        <v>428</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>26</v>
@@ -5077,27 +5088,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" ht="50.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>26</v>
@@ -5106,27 +5117,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" ht="50.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>26</v>
@@ -5135,27 +5146,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" ht="50.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>26</v>
@@ -5164,27 +5175,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" ht="50.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>26</v>
@@ -5193,27 +5204,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" ht="33.75" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>26</v>
@@ -5222,27 +5233,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" ht="33.75" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>26</v>
@@ -5251,27 +5262,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" ht="50.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>26</v>
@@ -5280,27 +5291,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" ht="50.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>26</v>
@@ -5309,27 +5320,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" ht="33.75" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>26</v>
@@ -5338,27 +5349,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" ht="50.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>518</v>
+        <v>488</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>26</v>
@@ -5367,27 +5378,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" ht="33.75" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>524</v>
+        <v>494</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>26</v>
@@ -5396,27 +5407,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" ht="50.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>26</v>
@@ -5425,27 +5436,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" ht="33.75" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>26</v>
@@ -5454,27 +5465,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" ht="50.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>542</v>
+        <v>512</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>26</v>
@@ -5483,27 +5494,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" ht="50.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>26</v>
@@ -5512,27 +5523,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" ht="50.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>26</v>
@@ -5541,27 +5552,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" ht="33.75" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>26</v>
@@ -5570,27 +5581,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" ht="33.75" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>26</v>
@@ -5599,27 +5610,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" ht="33.75" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>26</v>
@@ -5628,1459 +5639,1464 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" ht="50.25" customHeight="1">
       <c r="A91" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" ht="50.25" customHeight="1">
+      <c r="A92" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" ht="50.25" customHeight="1">
+      <c r="A93" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" ht="50.25" customHeight="1">
+      <c r="A94" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" ht="50.25" customHeight="1">
+      <c r="A95" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" ht="50.25" customHeight="1">
+      <c r="A96" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="B96" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="2" t="s">
+      <c r="C96" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" ht="50.25" customHeight="1">
+      <c r="A97" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="B97" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="2" t="s">
+      <c r="I97" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" ht="50.25" customHeight="1">
+      <c r="A98" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="2" t="s">
+      <c r="B98" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" ht="50.25" customHeight="1">
+      <c r="A99" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="2" t="s">
+      <c r="B99" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" ht="50.25" customHeight="1">
+      <c r="A100" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="2" t="s">
+      <c r="B100" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" ht="50.25" customHeight="1">
+      <c r="A101" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="2" t="s">
+      <c r="B101" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" ht="50.25" customHeight="1">
+      <c r="A102" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="2" t="s">
+      <c r="B102" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" ht="50.25" customHeight="1">
+      <c r="A103" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="2" t="s">
+      <c r="B103" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" ht="50.25" customHeight="1">
+      <c r="A104" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" ht="50.25" customHeight="1">
+      <c r="A105" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="2" t="s">
+      <c r="B105" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" ht="50.25" customHeight="1">
+      <c r="A106" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="2" t="s">
+      <c r="B106" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" ht="50.25" customHeight="1">
+      <c r="A107" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="2" t="s">
+      <c r="B107" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" ht="50.25" customHeight="1">
+      <c r="A108" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="2" t="s">
+      <c r="B108" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" ht="50.25" customHeight="1">
+      <c r="A109" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="2" t="s">
+      <c r="B109" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" ht="50.25" customHeight="1">
+      <c r="A110" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="2" t="s">
+      <c r="B110" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="2" t="s">
+      <c r="E110" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="2" t="s">
+      <c r="F110" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="2" t="s">
+      <c r="G110" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="H110" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" ht="66.75" customHeight="1">
       <c r="A111" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" ht="66.75" customHeight="1">
+      <c r="A112" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" ht="50.25" customHeight="1">
+      <c r="A113" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" ht="50.25" customHeight="1">
+      <c r="A114" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" ht="50.25" customHeight="1">
+      <c r="A115" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" ht="50.25" customHeight="1">
+      <c r="A116" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="2" t="s">
+      <c r="B116" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" ht="66.75" customHeight="1">
+      <c r="A117" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="2" t="s">
+      <c r="B117" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" ht="50.25" customHeight="1">
+      <c r="A118" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="2" t="s">
+      <c r="B118" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" ht="66.75" customHeight="1">
+      <c r="A119" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="2" t="s">
+      <c r="B119" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" ht="50.25" customHeight="1">
+      <c r="A120" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="2" t="s">
+      <c r="B120" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" ht="50.25" customHeight="1">
+      <c r="A121" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="2" t="s">
+      <c r="B121" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" ht="83.25" customHeight="1">
+      <c r="A122" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="2" t="s">
+      <c r="B122" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" ht="66.75" customHeight="1">
+      <c r="A123" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="2" t="s">
+      <c r="B123" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" ht="50.25" customHeight="1">
+      <c r="A124" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I119" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="2" t="s">
+      <c r="B124" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" ht="50.25" customHeight="1">
+      <c r="A125" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="2" t="s">
+      <c r="B125" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" ht="50.25" customHeight="1">
+      <c r="A126" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="83" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="2" t="s">
+      <c r="B126" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" ht="50.25" customHeight="1">
+      <c r="A127" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="2" t="s">
+      <c r="B127" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" ht="66.75" customHeight="1">
+      <c r="A128" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="2" t="s">
+      <c r="B128" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" ht="50.25" customHeight="1">
+      <c r="A129" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="2" t="s">
+      <c r="B129" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" ht="50.25" customHeight="1">
+      <c r="A130" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="2" t="s">
+      <c r="B130" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" ht="50.25" customHeight="1">
+      <c r="A131" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="2" t="s">
+      <c r="B131" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" ht="50.25" customHeight="1">
+      <c r="A132" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="2" t="s">
+      <c r="B132" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" ht="50.25" customHeight="1">
+      <c r="A133" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="2" t="s">
+      <c r="B133" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" ht="66.75" customHeight="1">
+      <c r="A134" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="2" t="s">
+      <c r="B134" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" ht="50.25" customHeight="1">
+      <c r="A135" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="2" t="s">
+      <c r="B135" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" ht="50.25" customHeight="1">
+      <c r="A136" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I131" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="2" t="s">
+      <c r="B136" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" ht="66.75" customHeight="1">
+      <c r="A137" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="2" t="s">
+      <c r="B137" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" ht="50.25" customHeight="1">
+      <c r="A138" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="2" t="s">
+      <c r="B138" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" ht="50.25" customHeight="1">
+      <c r="A139" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="2" t="s">
+      <c r="B139" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" ht="50.25" customHeight="1">
+      <c r="A140" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="2" t="s">
+      <c r="B140" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I136" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="2" t="s">
+      <c r="D140" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="2" t="s">
+      <c r="E140" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I138" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="2" t="s">
+      <c r="F140" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="2" t="s">
+      <c r="G140" s="2" t="s">
         <v>849</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>843</v>
-      </c>
       <c r="H140" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" pageOrder="downThenOver" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>